--- a/p6_deployment/data/spain/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/spain/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,14 +434,229 @@
           <t>copiado_avoid_nan</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bDmOFmNG</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>p2dFnNso</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>A7v4ruhp</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alvendiz l 
+  esp </t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Qkg2vOrk</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/p6_deployment/data/spain/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
+++ b/p6_deployment/data/spain/data_preparation/fill_data/df_copiado_ref_and_coaches.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,6 +658,110 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>IilCZTta</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>ng6idLW1</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">villanueva j  i 
+  esp </t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>bs5KnIiT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>CWcwKOO8</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>p2dFnNso</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
